--- a/Data/EffectMenu.xlsx
+++ b/Data/EffectMenu.xlsx
@@ -1,31 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CombatCalculatorTest\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D7846E-BFCF-48A6-BAE3-969BB632C5AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="4185" yWindow="960" windowWidth="23790" windowHeight="16320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="EffectGroup" sheetId="2" r:id="rId1"/>
-    <sheet name="EffectRow" sheetId="3" r:id="rId2"/>
+    <sheet state="visible" name="Info" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="EffectGroup" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="EffectRow" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="G1">
+      <text>
+        <t xml:space="preserve">TargetScope：Owner / Party / Enemy / AllEnemies</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="H1">
+      <text>
+        <t xml:space="preserve">Instant / TurnCount</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+  <si>
+    <t>EffectMenu：能力「發動後要做什麼」的行為腳本</t>
+  </si>
+  <si>
+    <t>分兩層：</t>
+  </si>
+  <si>
+    <t>EffectGroup：效果群組的執行模式</t>
+  </si>
   <si>
     <t>EffectGroupId</t>
   </si>
   <si>
+    <t>ExecMode（Sequential / Parallel / RandomPick…）</t>
+  </si>
+  <si>
+    <t>EffectRow：一條條要執行的效果</t>
+  </si>
+  <si>
+    <t>EffectType（AddStatus / DealDamage / Draw / ModifyStatTemp…）</t>
+  </si>
+  <si>
+    <t>Value1 / Value2：固定參數</t>
+  </si>
+  <si>
+    <t>ValueRefType / ValueRefId：動態取值來源（你這次新增的超關鍵）</t>
+  </si>
+  <si>
+    <t>EffectRow 才真的改變戰鬥狀態（加 buff、改數值、抽牌…）。</t>
+  </si>
+  <si>
     <t>ExecMode</t>
   </si>
   <si>
@@ -50,12 +89,27 @@
     <t>ValueRefId</t>
   </si>
   <si>
+    <t>TargetScope</t>
+  </si>
+  <si>
+    <t>DurationType</t>
+  </si>
+  <si>
+    <t>DurationValue</t>
+  </si>
+  <si>
     <t>AddStatus</t>
   </si>
   <si>
     <t>AttackUp</t>
   </si>
   <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>TurnCount</t>
+  </si>
+  <si>
     <t>SetStatusParam</t>
   </si>
   <si>
@@ -71,34 +125,26 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="2">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -106,42 +152,52 @@
         <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+  <cellXfs count="4">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -331,113 +387,195 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="18.140625" customWidth="1"/>
-  </cols>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="7">
+      <c r="B7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="9">
+      <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="11">
+      <c r="B11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="13">
+      <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="18.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="18.13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="18.13"/>
+    <col customWidth="1" min="2" max="2" width="13.13"/>
+    <col customWidth="1" min="6" max="6" width="17.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>1.0</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/Data/EffectMenu.xlsx
+++ b/Data/EffectMenu.xlsx
@@ -1,31 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CombatCalculatorTest\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7AF5040-DFA8-4301-844E-486AD4EB167F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Info" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="EffectGroup" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="EffectRow" sheetId="3" r:id="rId6"/>
+    <sheet name="Info" sheetId="1" r:id="rId1"/>
+    <sheet name="EffectGroup" sheetId="2" r:id="rId2"/>
+    <sheet name="EffectRow" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
+    <author>何巧薇</author>
   </authors>
   <commentList>
-    <comment authorId="0" ref="G1">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
-        <t xml:space="preserve">TargetScope：Owner / Party / Enemy / AllEnemies</t>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>TargetScope：Owner / Party / Enemy / AllEnemies</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="H1">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
-        <t xml:space="preserve">Instant / TurnCount</t>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Instant / TurnCount</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="1" shapeId="0" xr:uid="{F7312634-2823-49EB-881A-A65EFA9C258D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>何巧薇</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Max=3
+</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -33,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
   <si>
     <t>EffectMenu：能力「發動後要做什麼」的行為腳本</t>
   </si>
@@ -120,31 +182,110 @@
   </si>
   <si>
     <t>PartnerAttackIncrease</t>
+  </si>
+  <si>
+    <t>MobakoCheer</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EG_Arwen_BattleStartBuff</t>
+  </si>
+  <si>
+    <t>EG_Arwen_MitigateOnDamaged</t>
+  </si>
+  <si>
+    <t>PartnerStack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PartnerHealIncrease</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SetCheerStackByEnemyCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EG_Arwen_MitigateOnDamaged</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MitigateDamageAndConsumeCheer</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusStack</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Owner</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -158,46 +299,60 @@
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -387,82 +542,87 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="B7:B25"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="7">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.13"/>
+    <col min="1" max="1" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -470,7 +630,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -478,24 +638,43 @@
         <v>12</v>
       </c>
     </row>
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.13"/>
-    <col customWidth="1" min="2" max="2" width="13.13"/>
-    <col customWidth="1" min="6" max="6" width="17.5"/>
+    <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -509,73 +688,167 @@
         <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D2" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="E2" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
       <c r="F2" s="3"/>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="1">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="J2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="3"/>
       <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="1">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
     </row>
   </sheetData>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>